--- a/docs/all/idx12_salud_loadings_y_tops.xlsx
+++ b/docs/all/idx12_salud_loadings_y_tops.xlsx
@@ -396,10 +396,10 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.03769913565558838</v>
+        <v>0.03769913565558886</v>
       </c>
       <c r="D2">
-        <v>0.02237485084013417</v>
+        <v>0.02237485084013446</v>
       </c>
       <c r="E2">
         <v>2.2</v>
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.6906704953426398</v>
+        <v>0.6906704953426406</v>
       </c>
       <c r="D3">
-        <v>0.4099205205698757</v>
+        <v>0.4099205205698762</v>
       </c>
       <c r="E3">
         <v>41</v>
@@ -438,10 +438,10 @@
         </is>
       </c>
       <c r="C4">
-        <v>0.2992503984388554</v>
+        <v>0.299250398438855</v>
       </c>
       <c r="D4">
-        <v>0.1776083963858086</v>
+        <v>0.1776083963858084</v>
       </c>
       <c r="E4">
         <v>17.8</v>
@@ -459,10 +459,10 @@
         </is>
       </c>
       <c r="C5">
-        <v>0.6572687738423002</v>
+        <v>0.6572687738422991</v>
       </c>
       <c r="D5">
-        <v>0.3900962322041816</v>
+        <v>0.390096232204181</v>
       </c>
       <c r="E5">
         <v>39</v>
@@ -480,7 +480,7 @@
         </is>
       </c>
       <c r="C6">
-        <v>0.7689813484181395</v>
+        <v>0.7689813484181394</v>
       </c>
       <c r="D6">
         <v>0.4620138043326465</v>
@@ -501,10 +501,10 @@
         </is>
       </c>
       <c r="C7">
-        <v>-0.06368547385100178</v>
+        <v>-0.06368547385100198</v>
       </c>
       <c r="D7">
-        <v>0.03826304515077695</v>
+        <v>0.03826304515077707</v>
       </c>
       <c r="E7">
         <v>3.8</v>
@@ -522,7 +522,7 @@
         </is>
       </c>
       <c r="C8">
-        <v>0.5872082183855581</v>
+        <v>0.5872082183855579</v>
       </c>
       <c r="D8">
         <v>0.3528021888564541</v>
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="C9">
-        <v>-0.2445370206448342</v>
+        <v>-0.244537020644834</v>
       </c>
       <c r="D9">
-        <v>0.1469209616601225</v>
+        <v>0.1469209616601224</v>
       </c>
       <c r="E9">
         <v>14.7</v>
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="C10">
-        <v>0.6367424804894487</v>
+        <v>0.6367424804894485</v>
       </c>
       <c r="D10">
-        <v>0.3816523616783746</v>
+        <v>0.3816523616783747</v>
       </c>
       <c r="E10">
         <v>38.2</v>
@@ -585,10 +585,10 @@
         </is>
       </c>
       <c r="C11">
-        <v>0.08376438942665379</v>
+        <v>0.08376438942665332</v>
       </c>
       <c r="D11">
-        <v>0.05020691728413625</v>
+        <v>0.050206917284136</v>
       </c>
       <c r="E11">
         <v>5</v>
@@ -606,10 +606,10 @@
         </is>
       </c>
       <c r="C12">
-        <v>-0.7369093329479377</v>
+        <v>-0.7369093329479378</v>
       </c>
       <c r="D12">
-        <v>0.4416906298543662</v>
+        <v>0.4416906298543666</v>
       </c>
       <c r="E12">
         <v>44.2</v>
@@ -627,10 +627,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.2109672382583369</v>
+        <v>0.2109672382583363</v>
       </c>
       <c r="D13">
-        <v>0.1264500911831229</v>
+        <v>0.1264500911831226</v>
       </c>
       <c r="E13">
         <v>12.6</v>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.0424908754438582</v>
+        <v>0.04249087544385819</v>
       </c>
       <c r="D14">
         <v>0.02673647089698697</v>
@@ -669,10 +669,10 @@
         </is>
       </c>
       <c r="C15">
-        <v>-0.7154732380372489</v>
+        <v>-0.7154732380372482</v>
       </c>
       <c r="D15">
-        <v>0.4501961705079661</v>
+        <v>0.4501961705079656</v>
       </c>
       <c r="E15">
         <v>45</v>
@@ -693,7 +693,7 @@
         <v>0.1503341022817873</v>
       </c>
       <c r="D16">
-        <v>0.09459450549077</v>
+        <v>0.09459450549077002</v>
       </c>
       <c r="E16">
         <v>9.5</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C17">
-        <v>0.6809495053582446</v>
+        <v>0.6809495053582455</v>
       </c>
       <c r="D17">
-        <v>0.4284728531042769</v>
+        <v>0.4284728531042774</v>
       </c>
       <c r="E17">
         <v>42.8</v>
@@ -749,7 +749,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.3985083393198149</v>
+        <v>0.3985083393198152</v>
       </c>
     </row>
     <row r="3">
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.2728732106366015</v>
+        <v>0.2728732106366013</v>
       </c>
     </row>
     <row r="4">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.6906704953426398</v>
+        <v>0.6906704953426406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.6572687738423002</v>
+        <v>0.6572687738422991</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -846,7 +846,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.2992503984388554</v>
+        <v>0.299250398438855</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.03769913565558838</v>
+        <v>0.03769913565558886</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         </is>
       </c>
       <c r="B2">
-        <v>0.7689813484181395</v>
+        <v>0.7689813484181394</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -918,7 +918,7 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.5872082183855581</v>
+        <v>0.5872082183855579</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.2445370206448342</v>
+        <v>-0.244537020644834</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -948,7 +948,7 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.06368547385100178</v>
+        <v>-0.06368547385100198</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
